--- a/Project_Master_Dataset_and_Results.xlsx
+++ b/Project_Master_Dataset_and_Results.xlsx
@@ -7,13 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1_Groundwater_Dataset" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2_Model_Benchmarks" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3_BIS_IS_10500_Standards" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4_LOOCV_Spatial_Kriging" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5_Anomaly_Spike_Scenarios" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6_Literature_Validation" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7_Batch_Screening_Outputs" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Data Set" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tables" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Figures" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Outputs" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,12 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="+0.000"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -149,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -208,17 +204,11 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -228,6 +218,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -304,6 +297,161 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4286250" cy="2333625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4286250" cy="3333750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4286250" cy="3238500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="2476500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -596,7 +744,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S91"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
@@ -622,7 +770,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GROUNDWATER HEAVY METAL INTELLIGENCE SYSTEM (GHMIS) - RESEARCH DATASET (N = 88)</t>
+          <t>GROUNDWATER HEAVY METAL INTELLIGENCE SYSTEM (GHMIS) - RESEARCH DATA SET (N = 88)</t>
         </is>
       </c>
     </row>
@@ -6458,96 +6606,74 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>RESEARCH TABLES: BENCHMARKS, STANDARDS, SPATIAL LOOCV &amp; VALIDATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
           <t>TABLE 1: 5-FOLD CROSS-VALIDATION SURROGATE MODEL BENCHMARKS</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Algorithm / Model Family</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Algorithm / Model</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Target Variable</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>5-Fold R² Mean</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>R² Std (±)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>MAE</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>RMSE</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Evaluation Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Gradient Boosting Regressor</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>HPI (Pollution Index)</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="n">
-        <v>0.9305</v>
-      </c>
-      <c r="D4" s="20" t="n">
-        <v>0.0312</v>
-      </c>
-      <c r="E4" s="20" t="n">
-        <v>4.3836</v>
-      </c>
-      <c r="F4" s="20" t="n">
-        <v>5.7513</v>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Selected (Surrogate Engine)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>Random Forest Regressor</t>
+          <t>Gradient Boosting Regressor</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
@@ -6556,27 +6682,27 @@
         </is>
       </c>
       <c r="C5" s="21" t="n">
-        <v>0.9166</v>
+        <v>0.9305</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>0.0272</v>
+        <v>0.0312</v>
       </c>
       <c r="E5" s="21" t="n">
-        <v>4.7084</v>
+        <v>4.3836</v>
       </c>
       <c r="F5" s="21" t="n">
-        <v>6.2942</v>
+        <v>5.7513</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>Selected (Field Proxy)</t>
+          <t>Selected (Surrogate Engine)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Ridge Regressor (L2)</t>
+          <t>Random Forest Regressor</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -6584,28 +6710,28 @@
           <t>HPI (Pollution Index)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="n">
-        <v>0.846</v>
-      </c>
-      <c r="D6" s="20" t="n">
-        <v>0.0354</v>
-      </c>
-      <c r="E6" s="20" t="n">
-        <v>6.9182</v>
-      </c>
-      <c r="F6" s="20" t="n">
-        <v>8.7507</v>
+      <c r="C6" s="22" t="n">
+        <v>0.9166</v>
+      </c>
+      <c r="D6" s="22" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="E6" s="22" t="n">
+        <v>4.7084</v>
+      </c>
+      <c r="F6" s="22" t="n">
+        <v>6.2942</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Baseline Comparison</t>
+          <t>Selected (Field Proxy)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>Support Vector Regressor (SVR)</t>
+          <t>Ridge Regressor (L2)</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
@@ -6614,177 +6740,731 @@
         </is>
       </c>
       <c r="C7" s="21" t="n">
-        <v>0.0612</v>
+        <v>0.846</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>0.0888</v>
+        <v>0.0354</v>
       </c>
       <c r="E7" s="21" t="n">
-        <v>15.7073</v>
+        <v>6.9182</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>21.9975</v>
+        <v>8.7507</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>Discarded (Non-linear Failure)</t>
+          <t>Baseline Comparison</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Proxy Cadmium Regressor (RF)</t>
+          <t>Support Vector Regressor (SVR)</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cadmium (Cd in mg/L)</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="n">
-        <v>0.9119</v>
-      </c>
-      <c r="D8" s="20" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>0.0004</v>
+          <t>HPI (Pollution Index)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="n">
+        <v>0.0612</v>
+      </c>
+      <c r="D8" s="22" t="n">
+        <v>0.0888</v>
+      </c>
+      <c r="E8" s="22" t="n">
+        <v>15.7073</v>
+      </c>
+      <c r="F8" s="22" t="n">
+        <v>21.9975</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Deployed (Direct Risk Target)</t>
+          <t>Discarded (Non-linear Failure)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>Proxy Manganese Regressor (RF)</t>
+          <t>Proxy Cadmium Regressor (RF)</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Manganese (Mn in mg/L)</t>
+          <t>Cadmium (Cd in mg/L)</t>
         </is>
       </c>
       <c r="C9" s="21" t="n">
-        <v>0.6016</v>
+        <v>0.9119</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="E9" s="21" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="F9" s="21" t="n">
-        <v>0.045</v>
+        <v>0.034</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>0.0004</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>Deployed (Secondary Target)</t>
+          <t>Deployed (Direct Risk Target)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
+          <t>Proxy Manganese Regressor (RF)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Manganese (Mn in mg/L)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="n">
+        <v>0.6016</v>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="E10" s="22" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="F10" s="22" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Deployed (Secondary Target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
           <t>Proxy Iron Regressor (RF)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Iron (Fe in mg/L)</t>
         </is>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C11" s="21" t="n">
         <v>0.3925</v>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D11" s="21" t="n">
         <v>0.052</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E11" s="21" t="n">
         <v>0.082</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F11" s="21" t="n">
         <v>0.114</v>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>Aesthetic Tracer Target</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12"/>
-    <row r="13">
-      <c r="A13" s="22" t="inlineStr">
-        <is>
-          <t>TABLE 2: SAFETY CATEGORY CLASSIFICATION BENCHMARK</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Classifier Architecture</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Accuracy (%)</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Weighted F1 Score</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Cross-Validation</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Random Forest Classifier (150 trees)</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Safe / Moderate / Polluted</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>82.75</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>0.822</v>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>5-Fold Stratified CV</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Deployed (Field Triage)</t>
-        </is>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>TABLE 2: INDIAN STANDARD DRINKING WATER SPECIFICATION (BIS IS 10500:2012)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Element Name</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Permissible Si (mg/L)</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Ideal Ii (mg/L)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>MAC (mg/L)</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Toxicity Weight Wi</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Biological Health Impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Cd</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Cadmium</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>333.3333</v>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Renal dysfunction, Itai-Itai bone demineralization, kidney failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>Neurotoxicity, cognitive delay in children, anemia, hypertension</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Contact dermatitis, allergic eczema, gastrointestinal irritation</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>Liver cirrhosis in excess, gastrointestinal cramps, Wilson's disease</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Manganese</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Parkinsonian motor deficit (Manganism), neurological impairment</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <v>3.3333</v>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>Hemochromatosis, astringent metallic taste, pipe encrustation</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Zn</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Astringent taste, competitive copper deficiency at high levels</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>TABLE 3: ORDINARY KRIGING LEAVE-ONE-OUT CROSS-VALIDATION (LOOCV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Hydrological Cycle</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Stations (N)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Variogram Model</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Spatial R² Score</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Mean Error (Bias)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>Post-Monsoon (Surveillance Leaching Cycle)</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Spherical</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>0.4903</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>17.847</v>
+      </c>
+      <c r="F27" s="16" t="n">
+        <v>13.3151</v>
+      </c>
+      <c r="G27" s="16" t="n">
+        <v>-1.085</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Pre-Monsoon (Summer Baseline Cycle)</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Spherical</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>5.3263</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>-0.1844</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>Cross-Seasonal Composite Mean</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>88</v>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Spherical</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>0.3937</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>11.5867</v>
+      </c>
+      <c r="F29" s="16" t="n">
+        <v>8.8675</v>
+      </c>
+      <c r="G29" s="16" t="n">
+        <v>-0.6347</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Literature Reported Benchmark (Kadaladi Block)</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Spherical (nlags=8)</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>18.159</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G30" s="8" t="n">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>TABLE 4: LITERATURE BENCHMARK CONCORDANCE (NARAYANAN ET AL., 2021)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Station ID</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Reference Location Name</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Geographic Coordinates</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Published HPI</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>GHMIS HPI</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Absolute Diff</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Percentage Deviation (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>REF_LOC_01</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Sayalgudi Coastal Borewell (Station 3)</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>9.2106°N, 78.3941°E</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>33.58</v>
+      </c>
+      <c r="F35" s="16" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G35" s="16" t="n">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>REF_LOC_02</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Mudukulathur Agriculture Well (Station 2)</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>9.3615°N, 78.4504°E</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>25.74</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>REF_LOC_03</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>Kadaladi Town Monitoring Well (Station 14)</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>9.2406°N, 78.5750°E</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="F37" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G37" s="16" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>REF_LOC_04</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Valinokkam Marine Boundary (Station 25)</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>9.1747°N, 78.5096°E</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>41.35</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
+          <t>COMPOSITE</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>OVERALL BENCHMARK AVERAGE</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>Kadaladi Coastal Aquifer Tract</t>
+        </is>
+      </c>
+      <c r="D39" s="25" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="E39" s="25" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="F39" s="25" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G39" s="25" t="n">
+        <v>2.12</v>
       </c>
     </row>
   </sheetData>
@@ -6801,312 +7481,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLE 3: INDIAN STANDARD DRINKING WATER SPECIFICATION (BIS IS 10500:2012 / WHO)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Symbol</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Element Name</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Permissible Limit Si (mg/L)</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Ideal Limit Ii (mg/L)</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Upper Threshold MAC (mg/L)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Unit Weight Wi</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Biological Health Impact</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Toxicological Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Cd</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Cadmium</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F4" s="8" t="n">
-        <v>333.3333</v>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Renal dysfunction, Itai-Itai bone demineralization, kidney failure</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Group 1 Carcinogen</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Pb</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>Lead</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>100</v>
-      </c>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>Neurotoxicity, cognitive delay in children, anemia, hypertension</t>
-        </is>
-      </c>
-      <c r="H5" s="14" t="inlineStr">
-        <is>
-          <t>Cumulative Toxicant</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Ni</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Nickel</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Contact dermatitis, allergic eczema, gastrointestinal irritation</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Trace Toxicant</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Cu</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>Liver cirrhosis in excess, gastrointestinal cramps, Wilson's disease</t>
-        </is>
-      </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>Essential Micronutrient</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Mn</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Manganese</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Parkinsonian motor deficit (Manganism), neurological impairment</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Neurotoxicant</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>Fe</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>3.3333</v>
-      </c>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>Hemochromatosis, astringent metallic taste, pipe encrustation</t>
-        </is>
-      </c>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t>Aesthetic &amp; Organ Load</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Zn</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Astringent taste, competitive copper deficiency at high levels</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>Essential Mineral</t>
+          <t>PROJECT FIGURES &amp; DATA VISUALIZATIONS (EMBEDDED HIGH-RES CHARTS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>Figure 1: Analog Polar HPI Speedometer Gauge</t>
+        </is>
+      </c>
+      <c r="H3" s="20" t="inlineStr">
+        <is>
+          <t>Figure 2: 7-Heavy Metal Radar / Spider Chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>Figure 3: Spatial Ordinary Kriging Contamination Map</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>Figure 4: Explainable AI - SHAP Local Waterfall Plot</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>Figure 5: SHAP Global Feature Impact Bar Chart</t>
+        </is>
+      </c>
+      <c r="H41" s="20" t="inlineStr">
+        <is>
+          <t>Figure 6: Multi-Model 5-Fold R² Regressor Comparison</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7116,738 +7542,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>TABLE 4: ORDINARY KRIGING LEAVE-ONE-OUT CROSS-VALIDATION (LOOCV) METRICS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Hydrological Cycle</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Stations (N)</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Variogram Model</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Spatial R² Score</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>RMSE</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>MAE</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mean Error (Bias)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Post-Monsoon (Surveillance Leaching Cycle)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Spherical</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>0.4903</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>17.847</v>
-      </c>
-      <c r="F4" s="8" t="n">
-        <v>13.3151</v>
-      </c>
-      <c r="G4" s="8" t="n">
-        <v>-1.085</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>Pre-Monsoon (Summer Baseline Cycle)</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="n">
-        <v>44</v>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Spherical</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>0.2971</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>5.3263</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>-0.1844</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Cross-Seasonal Composite Mean</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Spherical</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0.3937</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>11.5867</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>8.8675</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>-0.6347</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>Literature Benchmark Range (Kadaladi Block)</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="n">
-        <v>44</v>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Spherical (nlags=8)</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>18.159</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>-0.31</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="31" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>TABLE 5: 6 SIMULATED INDUSTRIAL CONTAMINATION SPIKE SCENARIOS BENCHMARK</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Scenario ID</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Contamination Incident Name</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Distinguishing Signature</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>IsoForest Score</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>IsoForest Alone</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>BIS Violations</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Dual-Layer Hybrid Alert</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>SCEN_01</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Industrial Electroplating Cadmium Discharge</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Toxic Dumping</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Cd = 0.045 mg/L (15x limit), pH = 6.1</t>
-        </is>
-      </c>
-      <c r="E4" s="23" t="n">
-        <v>-0.632</v>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>CAUGHT (Anomaly)</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Cd, pH, TDS</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>FLAGGED (Threat Intercepted)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>SCEN_02</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>Subtle Non-Point Source Cadmium Leaching</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>Sub-acute Leaching</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>Cd = 0.007 mg/L (2.3x limit), neutral pH 7.4</t>
-        </is>
-      </c>
-      <c r="E5" s="24" t="n">
-        <v>-0.513</v>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>MISSED (Within Bounds)</t>
-        </is>
-      </c>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>Cd &gt; 0.003</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>FLAGGED (Threat Intercepted)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>SCEN_03</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Acid Mine &amp; Soil Pyrite Drainage</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Acid Drainage</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Fe = 3.5 mg/L, Mn = 1.2 mg/L, pH = 5.1</t>
-        </is>
-      </c>
-      <c r="E6" s="23" t="n">
-        <v>-0.638</v>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>CAUGHT (Anomaly)</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Fe, Mn, pH, TDS</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>FLAGGED (Threat Intercepted)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>SCEN_04</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>Domestic Plumbing Pipe Rust Intrusion</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Pipe Corrosion</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Fe = 0.45 mg/L (1.5x limit), normal TDS/EC</t>
-        </is>
-      </c>
-      <c r="E7" s="24" t="n">
-        <v>-0.474</v>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>MISSED (Within Bounds)</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>Fe &gt; 0.3</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>FLAGGED (Threat Intercepted)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>SCEN_05</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Severe Coastal Storm Surge / Hypersaline Ingress</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Salinity Shock</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>TDS = 4800 mg/L, EC = 7200 µS/cm</t>
-        </is>
-      </c>
-      <c r="E8" s="23" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>MISSED (Near Threshold)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>TDS, Mn</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>FLAGGED (Threat Intercepted)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>SCEN_06</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>Agricultural Seasonal Fertilizer Runoff</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>Agro-Mineral Shift</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>TDS = 650 mg/L, EC = 980 µS/cm, compliant metals</t>
-        </is>
-      </c>
-      <c r="E9" s="24" t="n">
-        <v>-0.419</v>
-      </c>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>MISSED (Safe Matrix)</t>
-        </is>
-      </c>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H9" s="11" t="inlineStr">
-        <is>
-          <t>NORMAL (No Action Required)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>TABLE 6: LITERATURE BENCHMARK CONCORDANCE (NARAYANAN ET AL., 2021)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Station ID</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Reference Location Name</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Geographic Coordinates</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Published Literature HPI</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>GHMIS Calculated HPI</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Absolute Difference</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Percentage Deviation (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>REF_LOC_01</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Sayalgudi Coastal Borewell (Station 3)</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>9.2106°N, 78.3941°E</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>33.58</v>
-      </c>
-      <c r="F4" s="8" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="G4" s="8" t="n">
-        <v>2.68</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>REF_LOC_02</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>Mudukulathur Agriculture Well (Station 2)</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>9.3615°N, 78.4504°E</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="n">
-        <v>25.35</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>25.74</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>1.54</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>REF_LOC_03</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Kadaladi Town Monitoring Well (Station 14)</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>9.2406°N, 78.5750°E</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>1.61</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>REF_LOC_04</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>Valinokkam Marine Boundary (Station 25)</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>9.1747°N, 78.5096°E</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="n">
-        <v>40.28</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>41.35</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>2.65</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="25" t="inlineStr">
-        <is>
-          <t>COMPOSITE</t>
-        </is>
-      </c>
-      <c r="B8" s="26" t="inlineStr">
-        <is>
-          <t>OVERALL BENCHMARK AVERAGE</t>
-        </is>
-      </c>
-      <c r="C8" s="26" t="inlineStr">
-        <is>
-          <t>Kadaladi Coastal Aquifer Tract</t>
-        </is>
-      </c>
-      <c r="D8" s="27" t="n">
-        <v>32.81</v>
-      </c>
-      <c r="E8" s="27" t="n">
-        <v>33.07</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>2.12</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K47"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:M91"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="33" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLE 7: BATCH SCREENING FIELD OUTPUTS &amp; REMEDIATION SPECIFICATIONS</t>
+          <t>TABLE 7: BATCH SCREENING OUTPUTS, HEALTH HAZARD INDICES &amp; REMEDIATION PLANS</t>
         </is>
       </c>
     </row>
@@ -7890,12 +7606,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Calculated HPI</t>
+          <t>HPI Output</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Calculated HEI</t>
+          <t>HEI Output</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -7905,7 +7621,17 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Recommended Remediation Action</t>
+          <t>Child Hazard Index (HI)</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Remediation Action Plan</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Est Cost (₹/kL)</t>
         </is>
       </c>
     </row>
@@ -7946,10 +7672,16 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>Activated Carbon + Sand Filter</t>
-        </is>
+      <c r="K4" s="8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="5">
@@ -7989,10 +7721,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K5" s="14" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K5" s="16" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L5" s="14" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M5" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8032,10 +7770,16 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>Activated Carbon + Sand Filter</t>
-        </is>
+      <c r="K6" s="8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="7">
@@ -8075,10 +7819,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K7" s="14" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K7" s="16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L7" s="14" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M7" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -8118,10 +7868,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K8" s="8" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -8161,10 +7917,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K9" s="14" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K9" s="16" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L9" s="14" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -8204,10 +7966,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K10" s="8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -8247,10 +8015,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K11" s="14" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K11" s="16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L11" s="14" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M11" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -8290,10 +8064,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K12" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -8333,10 +8113,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K13" s="14" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K13" s="16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L13" s="14" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M13" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -8376,10 +8162,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K14" s="6" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K14" s="8" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -8419,10 +8211,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K15" s="14" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K15" s="16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L15" s="14" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M15" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -8462,10 +8260,16 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="K16" s="6" t="inlineStr">
-        <is>
-          <t>Activated Carbon + Sand Filter</t>
-        </is>
+      <c r="K16" s="8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="17">
@@ -8505,10 +8309,16 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="K17" s="14" t="inlineStr">
-        <is>
-          <t>Activated Carbon + Sand Filter</t>
-        </is>
+      <c r="K17" s="16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L17" s="14" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M17" s="16" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="18">
@@ -8548,10 +8358,16 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="K18" s="6" t="inlineStr">
-        <is>
-          <t>Activated Carbon + Sand Filter</t>
-        </is>
+      <c r="K18" s="8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="19">
@@ -8591,10 +8407,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K19" s="14" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K19" s="16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L19" s="14" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M19" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -8634,10 +8456,16 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>Activated Carbon + Sand Filter</t>
-        </is>
+      <c r="K20" s="8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="21">
@@ -8677,10 +8505,16 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="K21" s="14" t="inlineStr">
-        <is>
-          <t>Activated Carbon + Sand Filter</t>
-        </is>
+      <c r="K21" s="16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L21" s="14" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M21" s="16" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="22">
@@ -8720,10 +8554,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K22" s="6" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K22" s="8" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -8763,10 +8603,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K23" s="14" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K23" s="16" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L23" s="14" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M23" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -8806,10 +8652,16 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="K24" s="6" t="inlineStr">
-        <is>
-          <t>Activated Carbon + Sand Filter</t>
-        </is>
+      <c r="K24" s="8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="25">
@@ -8849,10 +8701,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K25" s="14" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K25" s="16" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L25" s="14" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M25" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -8892,10 +8750,16 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="K26" s="6" t="inlineStr">
-        <is>
-          <t>Activated Carbon + Sand Filter</t>
-        </is>
+      <c r="K26" s="8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="27">
@@ -8935,10 +8799,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K27" s="14" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K27" s="16" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L27" s="14" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M27" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -8978,10 +8848,16 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="K28" s="6" t="inlineStr">
-        <is>
-          <t>Activated Carbon + Sand Filter</t>
-        </is>
+      <c r="K28" s="8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="29">
@@ -9021,10 +8897,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K29" s="14" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K29" s="16" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L29" s="14" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M29" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -9064,10 +8946,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K30" s="6" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K30" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -9107,10 +8995,16 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="K31" s="14" t="inlineStr">
-        <is>
-          <t>Activated Carbon + Sand Filter</t>
-        </is>
+      <c r="K31" s="16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L31" s="14" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M31" s="16" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="32">
@@ -9150,10 +9044,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K32" s="6" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K32" s="8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -9193,10 +9093,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K33" s="14" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K33" s="16" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L33" s="14" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M33" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -9236,10 +9142,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K34" s="6" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K34" s="8" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -9279,10 +9191,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K35" s="14" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K35" s="16" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L35" s="14" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M35" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -9322,10 +9240,16 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="K36" s="6" t="inlineStr">
-        <is>
-          <t>Activated Carbon + Sand Filter</t>
-        </is>
+      <c r="K36" s="8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="37">
@@ -9365,10 +9289,16 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="K37" s="14" t="inlineStr">
-        <is>
-          <t>Activated Carbon + Sand Filter</t>
-        </is>
+      <c r="K37" s="16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L37" s="14" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M37" s="16" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="38">
@@ -9408,10 +9338,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K38" s="6" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K38" s="8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M38" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -9451,10 +9387,16 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="K39" s="14" t="inlineStr">
-        <is>
-          <t>Activated Carbon + Sand Filter</t>
-        </is>
+      <c r="K39" s="16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L39" s="14" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M39" s="16" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="40">
@@ -9494,10 +9436,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K40" s="6" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K40" s="8" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M40" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -9537,10 +9485,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K41" s="14" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K41" s="16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L41" s="14" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M41" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -9580,10 +9534,16 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="K42" s="6" t="inlineStr">
-        <is>
-          <t>Activated Carbon + Sand Filter</t>
-        </is>
+      <c r="K42" s="8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M42" s="8" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="43">
@@ -9623,10 +9583,16 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="K43" s="14" t="inlineStr">
-        <is>
-          <t>Activated Carbon + Sand Filter</t>
-        </is>
+      <c r="K43" s="16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L43" s="14" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M43" s="16" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="44">
@@ -9666,10 +9632,16 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="K44" s="6" t="inlineStr">
-        <is>
-          <t>Activated Carbon + Sand Filter</t>
-        </is>
+      <c r="K44" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M44" s="8" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="45">
@@ -9709,10 +9681,16 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="K45" s="14" t="inlineStr">
-        <is>
-          <t>Activated Carbon + Sand Filter</t>
-        </is>
+      <c r="K45" s="16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L45" s="14" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M45" s="16" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="46">
@@ -9752,10 +9730,16 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K46" s="6" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K46" s="8" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M46" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -9795,10 +9779,2172 @@
           <t>Safe</t>
         </is>
       </c>
-      <c r="K47" s="14" t="inlineStr">
-        <is>
-          <t>Potable - No Treatment</t>
-        </is>
+      <c r="K47" s="16" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L47" s="14" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M47" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Location_1</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="n">
+        <v>9.157439999999999</v>
+      </c>
+      <c r="C48" s="8" t="n">
+        <v>78.56223300000001</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>1402.8</v>
+      </c>
+      <c r="G48" s="8" t="n">
+        <v>2003.4</v>
+      </c>
+      <c r="H48" s="8" t="n">
+        <v>70.70620746295303</v>
+      </c>
+      <c r="I48" s="8" t="n">
+        <v>3.548146666666666</v>
+      </c>
+      <c r="J48" s="26" t="inlineStr">
+        <is>
+          <t>Highly Polluted</t>
+        </is>
+      </c>
+      <c r="K48" s="8" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="L48" s="6" t="inlineStr">
+        <is>
+          <t>Lime Coagulation Softening + RO Desalination</t>
+        </is>
+      </c>
+      <c r="M48" s="8" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>Location_2</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="n">
+        <v>9.361542999999999</v>
+      </c>
+      <c r="C49" s="16" t="n">
+        <v>78.450458</v>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E49" s="16" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="F49" s="16" t="n">
+        <v>541.1</v>
+      </c>
+      <c r="G49" s="16" t="n">
+        <v>776.6</v>
+      </c>
+      <c r="H49" s="16" t="n">
+        <v>31.85727039814319</v>
+      </c>
+      <c r="I49" s="16" t="n">
+        <v>2.536206666666667</v>
+      </c>
+      <c r="J49" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K49" s="16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L49" s="14" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M49" s="16" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Location_3</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="n">
+        <v>9.210654999999999</v>
+      </c>
+      <c r="C50" s="8" t="n">
+        <v>78.394149</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="F50" s="8" t="n">
+        <v>1110.7</v>
+      </c>
+      <c r="G50" s="8" t="n">
+        <v>1665.7</v>
+      </c>
+      <c r="H50" s="8" t="n">
+        <v>59.9751495268702</v>
+      </c>
+      <c r="I50" s="8" t="n">
+        <v>4.050433333333333</v>
+      </c>
+      <c r="J50" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K50" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L50" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M50" s="8" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>Location_4</t>
+        </is>
+      </c>
+      <c r="B51" s="16" t="n">
+        <v>9.116343000000001</v>
+      </c>
+      <c r="C51" s="16" t="n">
+        <v>78.41907999999999</v>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E51" s="16" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="F51" s="16" t="n">
+        <v>1140.7</v>
+      </c>
+      <c r="G51" s="16" t="n">
+        <v>1692.6</v>
+      </c>
+      <c r="H51" s="16" t="n">
+        <v>47.54629592929834</v>
+      </c>
+      <c r="I51" s="16" t="n">
+        <v>3.03166</v>
+      </c>
+      <c r="J51" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K51" s="16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L51" s="14" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M51" s="16" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Location_5</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="n">
+        <v>9.296103</v>
+      </c>
+      <c r="C52" s="8" t="n">
+        <v>78.60876500000001</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="F52" s="8" t="n">
+        <v>806.1</v>
+      </c>
+      <c r="G52" s="8" t="n">
+        <v>1276</v>
+      </c>
+      <c r="H52" s="8" t="n">
+        <v>42.84044331369397</v>
+      </c>
+      <c r="I52" s="8" t="n">
+        <v>2.888013333333333</v>
+      </c>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K52" s="8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="L52" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M52" s="8" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>Location_6</t>
+        </is>
+      </c>
+      <c r="B53" s="16" t="n">
+        <v>9.212</v>
+      </c>
+      <c r="C53" s="16" t="n">
+        <v>78.47799999999999</v>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="F53" s="16" t="n">
+        <v>1954</v>
+      </c>
+      <c r="G53" s="16" t="n">
+        <v>2877.2</v>
+      </c>
+      <c r="H53" s="16" t="n">
+        <v>94.653387787895</v>
+      </c>
+      <c r="I53" s="16" t="n">
+        <v>6.654999999999999</v>
+      </c>
+      <c r="J53" s="26" t="inlineStr">
+        <is>
+          <t>Highly Polluted</t>
+        </is>
+      </c>
+      <c r="K53" s="16" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="L53" s="14" t="inlineStr">
+        <is>
+          <t>Lime Coagulation Softening + RO Desalination</t>
+        </is>
+      </c>
+      <c r="M53" s="16" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Location_7</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="n">
+        <v>9.387568999999999</v>
+      </c>
+      <c r="C54" s="8" t="n">
+        <v>78.560523</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="F54" s="8" t="n">
+        <v>406</v>
+      </c>
+      <c r="G54" s="8" t="n">
+        <v>615.5</v>
+      </c>
+      <c r="H54" s="8" t="n">
+        <v>24.43397304052847</v>
+      </c>
+      <c r="I54" s="8" t="n">
+        <v>1.779613333333333</v>
+      </c>
+      <c r="J54" s="18" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="K54" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L54" s="6" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M54" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>Location_8</t>
+        </is>
+      </c>
+      <c r="B55" s="16" t="n">
+        <v>9.327677</v>
+      </c>
+      <c r="C55" s="16" t="n">
+        <v>78.375542</v>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="F55" s="16" t="n">
+        <v>615.5</v>
+      </c>
+      <c r="G55" s="16" t="n">
+        <v>939.5</v>
+      </c>
+      <c r="H55" s="16" t="n">
+        <v>40.6309395643635</v>
+      </c>
+      <c r="I55" s="16" t="n">
+        <v>2.385833333333333</v>
+      </c>
+      <c r="J55" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K55" s="16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="L55" s="14" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M55" s="16" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Location_9</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="n">
+        <v>9.081573000000001</v>
+      </c>
+      <c r="C56" s="8" t="n">
+        <v>78.39039200000001</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F56" s="8" t="n">
+        <v>428.9</v>
+      </c>
+      <c r="G56" s="8" t="n">
+        <v>601.6</v>
+      </c>
+      <c r="H56" s="8" t="n">
+        <v>31.85716041778253</v>
+      </c>
+      <c r="I56" s="8" t="n">
+        <v>2.49298</v>
+      </c>
+      <c r="J56" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K56" s="8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L56" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M56" s="8" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>Location_10</t>
+        </is>
+      </c>
+      <c r="B57" s="16" t="n">
+        <v>9.177661000000001</v>
+      </c>
+      <c r="C57" s="16" t="n">
+        <v>78.328315</v>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E57" s="16" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="F57" s="16" t="n">
+        <v>809.6</v>
+      </c>
+      <c r="G57" s="16" t="n">
+        <v>1240.9</v>
+      </c>
+      <c r="H57" s="16" t="n">
+        <v>38.95934475986431</v>
+      </c>
+      <c r="I57" s="16" t="n">
+        <v>2.957133333333333</v>
+      </c>
+      <c r="J57" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K57" s="16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="L57" s="14" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M57" s="16" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Location_11</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n">
+        <v>9.360021</v>
+      </c>
+      <c r="C58" s="8" t="n">
+        <v>78.51430999999999</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="F58" s="8" t="n">
+        <v>773.1</v>
+      </c>
+      <c r="G58" s="8" t="n">
+        <v>1109.9</v>
+      </c>
+      <c r="H58" s="8" t="n">
+        <v>31.15159203713623</v>
+      </c>
+      <c r="I58" s="8" t="n">
+        <v>2.190586666666666</v>
+      </c>
+      <c r="J58" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K58" s="8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L58" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M58" s="8" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>Location_12</t>
+        </is>
+      </c>
+      <c r="B59" s="16" t="n">
+        <v>9.391745999999999</v>
+      </c>
+      <c r="C59" s="16" t="n">
+        <v>78.46287</v>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="F59" s="16" t="n">
+        <v>688.1</v>
+      </c>
+      <c r="G59" s="16" t="n">
+        <v>1095.6</v>
+      </c>
+      <c r="H59" s="16" t="n">
+        <v>36.70019309051955</v>
+      </c>
+      <c r="I59" s="16" t="n">
+        <v>2.62714</v>
+      </c>
+      <c r="J59" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K59" s="16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L59" s="14" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M59" s="16" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Location_13</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="n">
+        <v>9.248513000000001</v>
+      </c>
+      <c r="C60" s="8" t="n">
+        <v>78.448548</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="F60" s="8" t="n">
+        <v>1604.3</v>
+      </c>
+      <c r="G60" s="8" t="n">
+        <v>2293.7</v>
+      </c>
+      <c r="H60" s="8" t="n">
+        <v>96.1010665952508</v>
+      </c>
+      <c r="I60" s="8" t="n">
+        <v>6.234906666666666</v>
+      </c>
+      <c r="J60" s="26" t="inlineStr">
+        <is>
+          <t>Highly Polluted</t>
+        </is>
+      </c>
+      <c r="K60" s="8" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="L60" s="6" t="inlineStr">
+        <is>
+          <t>Lime Coagulation Softening + RO Desalination</t>
+        </is>
+      </c>
+      <c r="M60" s="8" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>Location_14</t>
+        </is>
+      </c>
+      <c r="B61" s="16" t="n">
+        <v>9.240681</v>
+      </c>
+      <c r="C61" s="16" t="n">
+        <v>78.57501499999999</v>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="F61" s="16" t="n">
+        <v>990.7</v>
+      </c>
+      <c r="G61" s="16" t="n">
+        <v>1469.1</v>
+      </c>
+      <c r="H61" s="16" t="n">
+        <v>50.69485841813962</v>
+      </c>
+      <c r="I61" s="16" t="n">
+        <v>3.483053333333333</v>
+      </c>
+      <c r="J61" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K61" s="16" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="L61" s="14" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M61" s="16" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Location_15</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="n">
+        <v>9.237901000000001</v>
+      </c>
+      <c r="C62" s="8" t="n">
+        <v>78.53151800000001</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="F62" s="8" t="n">
+        <v>1742.2</v>
+      </c>
+      <c r="G62" s="8" t="n">
+        <v>2468.8</v>
+      </c>
+      <c r="H62" s="8" t="n">
+        <v>87.68816943402965</v>
+      </c>
+      <c r="I62" s="8" t="n">
+        <v>6.181786666666667</v>
+      </c>
+      <c r="J62" s="26" t="inlineStr">
+        <is>
+          <t>Highly Polluted</t>
+        </is>
+      </c>
+      <c r="K62" s="8" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="L62" s="6" t="inlineStr">
+        <is>
+          <t>Lime Coagulation Softening + RO Desalination</t>
+        </is>
+      </c>
+      <c r="M62" s="8" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>Location_16</t>
+        </is>
+      </c>
+      <c r="B63" s="16" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="C63" s="16" t="n">
+        <v>78.54000000000001</v>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E63" s="16" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="F63" s="16" t="n">
+        <v>534.5</v>
+      </c>
+      <c r="G63" s="16" t="n">
+        <v>854.9</v>
+      </c>
+      <c r="H63" s="16" t="n">
+        <v>25.58090073201214</v>
+      </c>
+      <c r="I63" s="16" t="n">
+        <v>1.288333333333333</v>
+      </c>
+      <c r="J63" s="18" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="K63" s="16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L63" s="14" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M63" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Location_17</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="n">
+        <v>9.18449</v>
+      </c>
+      <c r="C64" s="8" t="n">
+        <v>78.60388</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="F64" s="8" t="n">
+        <v>861</v>
+      </c>
+      <c r="G64" s="8" t="n">
+        <v>1291.9</v>
+      </c>
+      <c r="H64" s="8" t="n">
+        <v>36.21290198178896</v>
+      </c>
+      <c r="I64" s="8" t="n">
+        <v>2.57984</v>
+      </c>
+      <c r="J64" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K64" s="8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L64" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M64" s="8" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>Location_18</t>
+        </is>
+      </c>
+      <c r="B65" s="16" t="n">
+        <v>9.129367999999999</v>
+      </c>
+      <c r="C65" s="16" t="n">
+        <v>78.481183</v>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="F65" s="16" t="n">
+        <v>1779.1</v>
+      </c>
+      <c r="G65" s="16" t="n">
+        <v>2702.6</v>
+      </c>
+      <c r="H65" s="16" t="n">
+        <v>94.11347205856096</v>
+      </c>
+      <c r="I65" s="16" t="n">
+        <v>5.084986666666666</v>
+      </c>
+      <c r="J65" s="26" t="inlineStr">
+        <is>
+          <t>Highly Polluted</t>
+        </is>
+      </c>
+      <c r="K65" s="16" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="L65" s="14" t="inlineStr">
+        <is>
+          <t>Lime Coagulation Softening + RO Desalination</t>
+        </is>
+      </c>
+      <c r="M65" s="16" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Location_19</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="n">
+        <v>9.072891</v>
+      </c>
+      <c r="C66" s="8" t="n">
+        <v>78.56531099999999</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="F66" s="8" t="n">
+        <v>531.1</v>
+      </c>
+      <c r="G66" s="8" t="n">
+        <v>750.7</v>
+      </c>
+      <c r="H66" s="8" t="n">
+        <v>32.50760185681128</v>
+      </c>
+      <c r="I66" s="8" t="n">
+        <v>3.122413333333333</v>
+      </c>
+      <c r="J66" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K66" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L66" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M66" s="8" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="14" t="inlineStr">
+        <is>
+          <t>Location_20</t>
+        </is>
+      </c>
+      <c r="B67" s="16" t="n">
+        <v>9.194459</v>
+      </c>
+      <c r="C67" s="16" t="n">
+        <v>78.602003</v>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E67" s="16" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="F67" s="16" t="n">
+        <v>1349.2</v>
+      </c>
+      <c r="G67" s="16" t="n">
+        <v>2091.2</v>
+      </c>
+      <c r="H67" s="16" t="n">
+        <v>64.47328914479557</v>
+      </c>
+      <c r="I67" s="16" t="n">
+        <v>4.097166666666666</v>
+      </c>
+      <c r="J67" s="26" t="inlineStr">
+        <is>
+          <t>Highly Polluted</t>
+        </is>
+      </c>
+      <c r="K67" s="16" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="L67" s="14" t="inlineStr">
+        <is>
+          <t>Lime Coagulation Softening + RO Desalination</t>
+        </is>
+      </c>
+      <c r="M67" s="16" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Location_21</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="n">
+        <v>9.149201</v>
+      </c>
+      <c r="C68" s="8" t="n">
+        <v>78.43310099999999</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F68" s="8" t="n">
+        <v>1133</v>
+      </c>
+      <c r="G68" s="8" t="n">
+        <v>1633.8</v>
+      </c>
+      <c r="H68" s="8" t="n">
+        <v>64.65624727727192</v>
+      </c>
+      <c r="I68" s="8" t="n">
+        <v>3.871093333333333</v>
+      </c>
+      <c r="J68" s="26" t="inlineStr">
+        <is>
+          <t>Highly Polluted</t>
+        </is>
+      </c>
+      <c r="K68" s="8" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="L68" s="6" t="inlineStr">
+        <is>
+          <t>Lime Coagulation Softening + RO Desalination</t>
+        </is>
+      </c>
+      <c r="M68" s="8" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="14" t="inlineStr">
+        <is>
+          <t>Location_22</t>
+        </is>
+      </c>
+      <c r="B69" s="16" t="n">
+        <v>9.306848</v>
+      </c>
+      <c r="C69" s="16" t="n">
+        <v>78.599941</v>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E69" s="16" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="F69" s="16" t="n">
+        <v>888.1</v>
+      </c>
+      <c r="G69" s="16" t="n">
+        <v>1402.9</v>
+      </c>
+      <c r="H69" s="16" t="n">
+        <v>49.54945643635065</v>
+      </c>
+      <c r="I69" s="16" t="n">
+        <v>2.952913333333333</v>
+      </c>
+      <c r="J69" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K69" s="16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="L69" s="14" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M69" s="16" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Location_23</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="n">
+        <v>9.204314999999999</v>
+      </c>
+      <c r="C70" s="8" t="n">
+        <v>78.562521</v>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="F70" s="8" t="n">
+        <v>1500.3</v>
+      </c>
+      <c r="G70" s="8" t="n">
+        <v>2162</v>
+      </c>
+      <c r="H70" s="8" t="n">
+        <v>83.14458784145685</v>
+      </c>
+      <c r="I70" s="8" t="n">
+        <v>4.67514</v>
+      </c>
+      <c r="J70" s="26" t="inlineStr">
+        <is>
+          <t>Highly Polluted</t>
+        </is>
+      </c>
+      <c r="K70" s="8" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="L70" s="6" t="inlineStr">
+        <is>
+          <t>Lime Coagulation Softening + RO Desalination</t>
+        </is>
+      </c>
+      <c r="M70" s="8" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="14" t="inlineStr">
+        <is>
+          <t>Location_24</t>
+        </is>
+      </c>
+      <c r="B71" s="16" t="n">
+        <v>9.208</v>
+      </c>
+      <c r="C71" s="16" t="n">
+        <v>78.48099999999999</v>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E71" s="16" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="F71" s="16" t="n">
+        <v>1897.2</v>
+      </c>
+      <c r="G71" s="16" t="n">
+        <v>2728.4</v>
+      </c>
+      <c r="H71" s="16" t="n">
+        <v>94.40789591144438</v>
+      </c>
+      <c r="I71" s="16" t="n">
+        <v>6.488333333333332</v>
+      </c>
+      <c r="J71" s="26" t="inlineStr">
+        <is>
+          <t>Highly Polluted</t>
+        </is>
+      </c>
+      <c r="K71" s="16" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="L71" s="14" t="inlineStr">
+        <is>
+          <t>Lime Coagulation Softening + RO Desalination</t>
+        </is>
+      </c>
+      <c r="M71" s="16" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Location_25</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="n">
+        <v>9.174713000000001</v>
+      </c>
+      <c r="C72" s="8" t="n">
+        <v>78.50966200000001</v>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F72" s="8" t="n">
+        <v>1878.8</v>
+      </c>
+      <c r="G72" s="8" t="n">
+        <v>2644.1</v>
+      </c>
+      <c r="H72" s="8" t="n">
+        <v>96.1657332619175</v>
+      </c>
+      <c r="I72" s="8" t="n">
+        <v>5.97232</v>
+      </c>
+      <c r="J72" s="26" t="inlineStr">
+        <is>
+          <t>Highly Polluted</t>
+        </is>
+      </c>
+      <c r="K72" s="8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L72" s="6" t="inlineStr">
+        <is>
+          <t>Lime Coagulation Softening + RO Desalination</t>
+        </is>
+      </c>
+      <c r="M72" s="8" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="14" t="inlineStr">
+        <is>
+          <t>Location_26</t>
+        </is>
+      </c>
+      <c r="B73" s="16" t="n">
+        <v>9.261200000000001</v>
+      </c>
+      <c r="C73" s="16" t="n">
+        <v>78.318044</v>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E73" s="16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F73" s="16" t="n">
+        <v>600.2</v>
+      </c>
+      <c r="G73" s="16" t="n">
+        <v>896.9</v>
+      </c>
+      <c r="H73" s="16" t="n">
+        <v>33.72112158543117</v>
+      </c>
+      <c r="I73" s="16" t="n">
+        <v>2.65752</v>
+      </c>
+      <c r="J73" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K73" s="16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L73" s="14" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M73" s="16" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Location_27</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="n">
+        <v>9.271188</v>
+      </c>
+      <c r="C74" s="8" t="n">
+        <v>78.649344</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="F74" s="8" t="n">
+        <v>728.2</v>
+      </c>
+      <c r="G74" s="8" t="n">
+        <v>1101.7</v>
+      </c>
+      <c r="H74" s="8" t="n">
+        <v>34.02078396714872</v>
+      </c>
+      <c r="I74" s="8" t="n">
+        <v>2.429493333333333</v>
+      </c>
+      <c r="J74" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K74" s="8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L74" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M74" s="8" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="14" t="inlineStr">
+        <is>
+          <t>Location_28</t>
+        </is>
+      </c>
+      <c r="B75" s="16" t="n">
+        <v>9.142080999999999</v>
+      </c>
+      <c r="C75" s="16" t="n">
+        <v>78.48869000000001</v>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E75" s="16" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="F75" s="16" t="n">
+        <v>1818.7</v>
+      </c>
+      <c r="G75" s="16" t="n">
+        <v>2570.1</v>
+      </c>
+      <c r="H75" s="16" t="n">
+        <v>97.6825207105874</v>
+      </c>
+      <c r="I75" s="16" t="n">
+        <v>5.639593333333332</v>
+      </c>
+      <c r="J75" s="26" t="inlineStr">
+        <is>
+          <t>Highly Polluted</t>
+        </is>
+      </c>
+      <c r="K75" s="16" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="L75" s="14" t="inlineStr">
+        <is>
+          <t>Lime Coagulation Softening + RO Desalination</t>
+        </is>
+      </c>
+      <c r="M75" s="16" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Location_29</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="n">
+        <v>9.218</v>
+      </c>
+      <c r="C76" s="8" t="n">
+        <v>78.465</v>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="F76" s="8" t="n">
+        <v>677.8</v>
+      </c>
+      <c r="G76" s="8" t="n">
+        <v>1054.1</v>
+      </c>
+      <c r="H76" s="8" t="n">
+        <v>42.63142742367435</v>
+      </c>
+      <c r="I76" s="8" t="n">
+        <v>3.955</v>
+      </c>
+      <c r="J76" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K76" s="8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="L76" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M76" s="8" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="14" t="inlineStr">
+        <is>
+          <t>Location_30</t>
+        </is>
+      </c>
+      <c r="B77" s="16" t="n">
+        <v>9.377670999999999</v>
+      </c>
+      <c r="C77" s="16" t="n">
+        <v>78.543705</v>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E77" s="16" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="F77" s="16" t="n">
+        <v>1105.6</v>
+      </c>
+      <c r="G77" s="16" t="n">
+        <v>1648.1</v>
+      </c>
+      <c r="H77" s="16" t="n">
+        <v>60.51978628816282</v>
+      </c>
+      <c r="I77" s="16" t="n">
+        <v>2.70468</v>
+      </c>
+      <c r="J77" s="26" t="inlineStr">
+        <is>
+          <t>Highly Polluted</t>
+        </is>
+      </c>
+      <c r="K77" s="16" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="L77" s="14" t="inlineStr">
+        <is>
+          <t>Lime Coagulation Softening + RO Desalination</t>
+        </is>
+      </c>
+      <c r="M77" s="16" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Location_31</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="n">
+        <v>9.103921</v>
+      </c>
+      <c r="C78" s="8" t="n">
+        <v>78.39945299999999</v>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="F78" s="8" t="n">
+        <v>358.8</v>
+      </c>
+      <c r="G78" s="8" t="n">
+        <v>540</v>
+      </c>
+      <c r="H78" s="8" t="n">
+        <v>32.49731797893233</v>
+      </c>
+      <c r="I78" s="8" t="n">
+        <v>2.694613333333333</v>
+      </c>
+      <c r="J78" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K78" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L78" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M78" s="8" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="14" t="inlineStr">
+        <is>
+          <t>Location_32</t>
+        </is>
+      </c>
+      <c r="B79" s="16" t="n">
+        <v>9.295596</v>
+      </c>
+      <c r="C79" s="16" t="n">
+        <v>78.633619</v>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E79" s="16" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="F79" s="16" t="n">
+        <v>1133</v>
+      </c>
+      <c r="G79" s="16" t="n">
+        <v>1686.1</v>
+      </c>
+      <c r="H79" s="16" t="n">
+        <v>48.70982146045348</v>
+      </c>
+      <c r="I79" s="16" t="n">
+        <v>3.498333333333333</v>
+      </c>
+      <c r="J79" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K79" s="16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L79" s="14" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M79" s="16" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Location_33</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="n">
+        <v>9.205</v>
+      </c>
+      <c r="C80" s="8" t="n">
+        <v>78.47</v>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="F80" s="8" t="n">
+        <v>1549.6</v>
+      </c>
+      <c r="G80" s="8" t="n">
+        <v>2293.6</v>
+      </c>
+      <c r="H80" s="8" t="n">
+        <v>99.60786020353508</v>
+      </c>
+      <c r="I80" s="8" t="n">
+        <v>7.055</v>
+      </c>
+      <c r="J80" s="26" t="inlineStr">
+        <is>
+          <t>Highly Polluted</t>
+        </is>
+      </c>
+      <c r="K80" s="8" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="L80" s="6" t="inlineStr">
+        <is>
+          <t>Lime Coagulation Softening + RO Desalination</t>
+        </is>
+      </c>
+      <c r="M80" s="8" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="14" t="inlineStr">
+        <is>
+          <t>Location_34</t>
+        </is>
+      </c>
+      <c r="B81" s="16" t="n">
+        <v>9.268476</v>
+      </c>
+      <c r="C81" s="16" t="n">
+        <v>78.48022899999999</v>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="F81" s="16" t="n">
+        <v>1445.6</v>
+      </c>
+      <c r="G81" s="16" t="n">
+        <v>2185.6</v>
+      </c>
+      <c r="H81" s="16" t="n">
+        <v>82.30291233708266</v>
+      </c>
+      <c r="I81" s="16" t="n">
+        <v>5.413586666666665</v>
+      </c>
+      <c r="J81" s="26" t="inlineStr">
+        <is>
+          <t>Highly Polluted</t>
+        </is>
+      </c>
+      <c r="K81" s="16" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="L81" s="14" t="inlineStr">
+        <is>
+          <t>Lime Coagulation Softening + RO Desalination</t>
+        </is>
+      </c>
+      <c r="M81" s="16" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Location_35</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="n">
+        <v>9.327267000000001</v>
+      </c>
+      <c r="C82" s="8" t="n">
+        <v>78.472447</v>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="F82" s="8" t="n">
+        <v>756.6</v>
+      </c>
+      <c r="G82" s="8" t="n">
+        <v>1082.7</v>
+      </c>
+      <c r="H82" s="8" t="n">
+        <v>39.04506159614354</v>
+      </c>
+      <c r="I82" s="8" t="n">
+        <v>3.1082</v>
+      </c>
+      <c r="J82" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K82" s="8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="L82" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M82" s="8" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="14" t="inlineStr">
+        <is>
+          <t>Location_36</t>
+        </is>
+      </c>
+      <c r="B83" s="16" t="n">
+        <v>9.243981</v>
+      </c>
+      <c r="C83" s="16" t="n">
+        <v>78.437663</v>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E83" s="16" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="F83" s="16" t="n">
+        <v>1743.9</v>
+      </c>
+      <c r="G83" s="16" t="n">
+        <v>2504.9</v>
+      </c>
+      <c r="H83" s="16" t="n">
+        <v>97.97847312979825</v>
+      </c>
+      <c r="I83" s="16" t="n">
+        <v>6.062746666666666</v>
+      </c>
+      <c r="J83" s="26" t="inlineStr">
+        <is>
+          <t>Highly Polluted</t>
+        </is>
+      </c>
+      <c r="K83" s="16" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="L83" s="14" t="inlineStr">
+        <is>
+          <t>Lime Coagulation Softening + RO Desalination</t>
+        </is>
+      </c>
+      <c r="M83" s="16" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>Location_37</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="n">
+        <v>9.165736000000001</v>
+      </c>
+      <c r="C84" s="8" t="n">
+        <v>78.656626</v>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F84" s="8" t="n">
+        <v>757.9</v>
+      </c>
+      <c r="G84" s="8" t="n">
+        <v>1191.7</v>
+      </c>
+      <c r="H84" s="8" t="n">
+        <v>38.70814176039992</v>
+      </c>
+      <c r="I84" s="8" t="n">
+        <v>2.696253333333333</v>
+      </c>
+      <c r="J84" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K84" s="8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L84" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M84" s="8" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="14" t="inlineStr">
+        <is>
+          <t>Location_38</t>
+        </is>
+      </c>
+      <c r="B85" s="16" t="n">
+        <v>9.338177999999999</v>
+      </c>
+      <c r="C85" s="16" t="n">
+        <v>78.579476</v>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F85" s="16" t="n">
+        <v>1129.4</v>
+      </c>
+      <c r="G85" s="16" t="n">
+        <v>1794.9</v>
+      </c>
+      <c r="H85" s="16" t="n">
+        <v>53.9704652740582</v>
+      </c>
+      <c r="I85" s="16" t="n">
+        <v>2.678693333333333</v>
+      </c>
+      <c r="J85" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K85" s="16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="L85" s="14" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M85" s="16" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Location_39</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="n">
+        <v>9.180421000000001</v>
+      </c>
+      <c r="C86" s="8" t="n">
+        <v>78.399276</v>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="F86" s="8" t="n">
+        <v>723.8</v>
+      </c>
+      <c r="G86" s="8" t="n">
+        <v>1067.4</v>
+      </c>
+      <c r="H86" s="8" t="n">
+        <v>53.30680066059632</v>
+      </c>
+      <c r="I86" s="8" t="n">
+        <v>3.944646666666667</v>
+      </c>
+      <c r="J86" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K86" s="8" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="L86" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M86" s="8" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="14" t="inlineStr">
+        <is>
+          <t>Location_40</t>
+        </is>
+      </c>
+      <c r="B87" s="16" t="n">
+        <v>9.179791</v>
+      </c>
+      <c r="C87" s="16" t="n">
+        <v>78.512998</v>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E87" s="16" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="F87" s="16" t="n">
+        <v>1922</v>
+      </c>
+      <c r="G87" s="16" t="n">
+        <v>2794.9</v>
+      </c>
+      <c r="H87" s="16" t="n">
+        <v>107.1928496697018</v>
+      </c>
+      <c r="I87" s="16" t="n">
+        <v>6.256826666666666</v>
+      </c>
+      <c r="J87" s="26" t="inlineStr">
+        <is>
+          <t>Highly Polluted</t>
+        </is>
+      </c>
+      <c r="K87" s="16" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="L87" s="14" t="inlineStr">
+        <is>
+          <t>Lime Coagulation Softening + RO Desalination</t>
+        </is>
+      </c>
+      <c r="M87" s="16" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>Location_41</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="n">
+        <v>9.294287000000001</v>
+      </c>
+      <c r="C88" s="8" t="n">
+        <v>78.567038</v>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="F88" s="8" t="n">
+        <v>675.6</v>
+      </c>
+      <c r="G88" s="8" t="n">
+        <v>1032.9</v>
+      </c>
+      <c r="H88" s="8" t="n">
+        <v>45.48553901089091</v>
+      </c>
+      <c r="I88" s="8" t="n">
+        <v>3.310306666666667</v>
+      </c>
+      <c r="J88" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K88" s="8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="L88" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M88" s="8" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="14" t="inlineStr">
+        <is>
+          <t>Location_42</t>
+        </is>
+      </c>
+      <c r="B89" s="16" t="n">
+        <v>9.119401999999999</v>
+      </c>
+      <c r="C89" s="16" t="n">
+        <v>78.499172</v>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E89" s="16" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="F89" s="16" t="n">
+        <v>1061.1</v>
+      </c>
+      <c r="G89" s="16" t="n">
+        <v>1572.3</v>
+      </c>
+      <c r="H89" s="16" t="n">
+        <v>51.0493821638993</v>
+      </c>
+      <c r="I89" s="16" t="n">
+        <v>3.61082</v>
+      </c>
+      <c r="J89" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K89" s="16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="L89" s="14" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M89" s="16" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>Location_43</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="n">
+        <v>9.372176</v>
+      </c>
+      <c r="C90" s="8" t="n">
+        <v>78.529622</v>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="F90" s="8" t="n">
+        <v>677.7</v>
+      </c>
+      <c r="G90" s="8" t="n">
+        <v>952.2</v>
+      </c>
+      <c r="H90" s="8" t="n">
+        <v>29.29151919300125</v>
+      </c>
+      <c r="I90" s="8" t="n">
+        <v>2.268306666666667</v>
+      </c>
+      <c r="J90" s="18" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="K90" s="8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L90" s="6" t="inlineStr">
+        <is>
+          <t>Potable - No Chemical Treatment Required</t>
+        </is>
+      </c>
+      <c r="M90" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="14" t="inlineStr">
+        <is>
+          <t>Location_44</t>
+        </is>
+      </c>
+      <c r="B91" s="16" t="n">
+        <v>9.343021</v>
+      </c>
+      <c r="C91" s="16" t="n">
+        <v>78.41692</v>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>Post-Monsoon</t>
+        </is>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="F91" s="16" t="n">
+        <v>684.3</v>
+      </c>
+      <c r="G91" s="16" t="n">
+        <v>979.4</v>
+      </c>
+      <c r="H91" s="16" t="n">
+        <v>51.84268103910016</v>
+      </c>
+      <c r="I91" s="16" t="n">
+        <v>2.55974</v>
+      </c>
+      <c r="J91" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K91" s="16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="L91" s="14" t="inlineStr">
+        <is>
+          <t>Multi-Media Carbon + Sand Filtration</t>
+        </is>
+      </c>
+      <c r="M91" s="16" t="n">
+        <v>16.5</v>
       </c>
     </row>
   </sheetData>

--- a/Project_Master_Dataset_and_Results.xlsx
+++ b/Project_Master_Dataset_and_Results.xlsx
@@ -7249,33 +7249,7 @@
         <v>-0.6347</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Literature Reported Benchmark (Kadaladi Block)</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Spherical (nlags=8)</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>18.159</v>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="G30" s="8" t="n">
-        <v>-0.31</v>
-      </c>
-    </row>
+    <row r="30"/>
     <row r="31"/>
     <row r="32"/>
     <row r="33">

--- a/Project_Master_Dataset_and_Results.xlsx
+++ b/Project_Master_Dataset_and_Results.xlsx
@@ -7255,7 +7255,7 @@
     <row r="33">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>TABLE 4: LITERATURE BENCHMARK CONCORDANCE (NARAYANAN ET AL., 2021)</t>
+          <t>TABLE 4: LITERATURE BENCHMARK CONCORDANCE (NARAYANAN ET AL., 2025 SCI REP)</t>
         </is>
       </c>
     </row>
@@ -7309,20 +7309,20 @@
       </c>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>9.2106°N, 78.3941°E</t>
+          <t>9.2107°N, 78.3941°E</t>
         </is>
       </c>
       <c r="D35" s="16" t="n">
-        <v>34.5</v>
+        <v>33.9</v>
       </c>
       <c r="E35" s="16" t="n">
         <v>33.58</v>
       </c>
       <c r="F35" s="16" t="n">
-        <v>0.92</v>
+        <v>0.32</v>
       </c>
       <c r="G35" s="16" t="n">
-        <v>2.68</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="36">
@@ -7338,20 +7338,20 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>9.3615°N, 78.4504°E</t>
+          <t>9.3615°N, 78.4505°E</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>25.35</v>
+        <v>24.86</v>
       </c>
       <c r="E36" s="8" t="n">
         <v>25.74</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0.39</v>
+        <v>0.88</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>1.54</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="37">
@@ -7367,20 +7367,20 @@
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>9.2406°N, 78.5750°E</t>
+          <t>9.2407°N, 78.5750°E</t>
         </is>
       </c>
       <c r="D37" s="16" t="n">
-        <v>31.1</v>
+        <v>30.53</v>
       </c>
       <c r="E37" s="16" t="n">
         <v>31.6</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>0.5</v>
+        <v>1.07</v>
       </c>
       <c r="G37" s="16" t="n">
-        <v>1.61</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="38">
@@ -7396,20 +7396,20 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>9.1747°N, 78.5096°E</t>
+          <t>9.1747°N, 78.5097°E</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>40.28</v>
+        <v>39.5</v>
       </c>
       <c r="E38" s="8" t="n">
         <v>41.35</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>1.07</v>
+        <v>1.85</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>2.65</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="39">
@@ -7429,16 +7429,16 @@
         </is>
       </c>
       <c r="D39" s="25" t="n">
-        <v>32.81</v>
+        <v>32.2</v>
       </c>
       <c r="E39" s="25" t="n">
         <v>33.07</v>
       </c>
       <c r="F39" s="25" t="n">
-        <v>0.72</v>
+        <v>1.03</v>
       </c>
       <c r="G39" s="25" t="n">
-        <v>2.12</v>
+        <v>3.17</v>
       </c>
     </row>
   </sheetData>
